--- a/ksoft/docs/records/Internacional_Expenses_Records.xlsx
+++ b/ksoft/docs/records/Internacional_Expenses_Records.xlsx
@@ -1863,13 +1863,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60D5A75E-8A63-4E0B-B2F4-14ED848A7C08}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B35E12-3AC3-47F3-8748-E34D4199F24B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8B5FC83-79C8-4658-88EF-7AFFC748C5AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82EBAF9C-C1BD-4CC6-9675-1EBD90D6B9CD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D01B4A6-0371-4530-9786-383A95CFB0C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4204210-85D7-4C80-87E3-D60287DF2923}"/>
 </file>
--- a/ksoft/docs/records/Internacional_Expenses_Records.xlsx
+++ b/ksoft/docs/records/Internacional_Expenses_Records.xlsx
@@ -1863,13 +1863,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B35E12-3AC3-47F3-8748-E34D4199F24B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60D5A75E-8A63-4E0B-B2F4-14ED848A7C08}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82EBAF9C-C1BD-4CC6-9675-1EBD90D6B9CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8B5FC83-79C8-4658-88EF-7AFFC748C5AA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4204210-85D7-4C80-87E3-D60287DF2923}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D01B4A6-0371-4530-9786-383A95CFB0C4}"/>
 </file>